--- a/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/DAT/DAT+50T+50EP+optim_purn/params_vs_psnr_analysis/DAT_hutcn_hyperopt_study_full.xlsx
+++ b/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/DAT/DAT+50T+50EP+optim_purn/params_vs_psnr_analysis/DAT_hutcn_hyperopt_study_full.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,50 +446,55 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>flops_G</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>hp_n_feats</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>hp_num_heads</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>hp_num_blocks</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>hp_window_size</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>hp_patch_size</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>hp_optimizer</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>hp_scheduler</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>hp_loss</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>hp_lr</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>hp_weight_decay</t>
         </is>
@@ -506,39 +511,42 @@
         <v>27.65851249694824</v>
       </c>
       <c r="D2" t="n">
+        <v>1.16176302</v>
+      </c>
+      <c r="E2" t="n">
         <v>88</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
       </c>
       <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
         <v>8</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>192</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>step</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>3.135775732257744e-05</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1.256277350380703e-05</v>
       </c>
     </row>
@@ -553,39 +561,42 @@
         <v>28.04580268859863</v>
       </c>
       <c r="D3" t="n">
+        <v>1.277049024</v>
+      </c>
+      <c r="E3" t="n">
         <v>96</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
         <v>160</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>step</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>3.385226783451975e-05</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>3.632486956676606e-05</v>
       </c>
     </row>
@@ -600,39 +611,42 @@
         <v>27.6333381652832</v>
       </c>
       <c r="D4" t="n">
+        <v>1.16176302</v>
+      </c>
+      <c r="E4" t="n">
         <v>88</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
         <v>8</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>192</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>step</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>3.135775732257744e-05</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>1.256277350380703e-05</v>
       </c>
     </row>
@@ -647,39 +661,42 @@
         <v>28.05669136047363</v>
       </c>
       <c r="D5" t="n">
+        <v>1.277049024</v>
+      </c>
+      <c r="E5" t="n">
         <v>96</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
         <v>160</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>step</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>3.385226783451975e-05</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3.632486956676606e-05</v>
       </c>
     </row>
@@ -694,39 +711,42 @@
         <v>29.12904663085937</v>
       </c>
       <c r="D6" t="n">
+        <v>1.999435968</v>
+      </c>
+      <c r="E6" t="n">
         <v>96</v>
       </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
       <c r="F6" t="n">
         <v>4</v>
       </c>
       <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
         <v>8</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>224</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>step</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.0002051259942215138</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>3.9459088111e-06</v>
       </c>
     </row>
@@ -741,39 +761,42 @@
         <v>29.32546653747558</v>
       </c>
       <c r="D7" t="n">
+        <v>0.75007872</v>
+      </c>
+      <c r="E7" t="n">
         <v>64</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
         <v>12</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>128</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>0.0002041033406525706</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>3.02961044282125e-05</v>
       </c>
     </row>
@@ -788,39 +811,42 @@
         <v>30.61105842590332</v>
       </c>
       <c r="D8" t="n">
+        <v>1.893046464</v>
+      </c>
+      <c r="E8" t="n">
         <v>96</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>12</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>192</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>0.0003284210350911732</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>4.149795789891592e-05</v>
       </c>
     </row>
@@ -835,39 +861,42 @@
         <v>28.45059852600098</v>
       </c>
       <c r="D9" t="n">
+        <v>2.53528542</v>
+      </c>
+      <c r="E9" t="n">
         <v>120</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>3</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>8</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>128</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>step</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>6.995363653959081e-05</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>7.991621920384356e-06</v>
       </c>
     </row>
@@ -882,39 +911,42 @@
         <v>27.87301712036133</v>
       </c>
       <c r="D10" t="n">
+        <v>0.90653112</v>
+      </c>
+      <c r="E10" t="n">
         <v>80</v>
       </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
       <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" t="n">
-        <v>4</v>
-      </c>
       <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
         <v>160</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>3.50748407899447e-05</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>3.627066608804412e-06</v>
       </c>
     </row>
@@ -929,39 +961,42 @@
         <v>27.85956382751465</v>
       </c>
       <c r="D11" t="n">
+        <v>0.75007872</v>
+      </c>
+      <c r="E11" t="n">
         <v>64</v>
       </c>
-      <c r="E11" t="n">
-        <v>4</v>
-      </c>
       <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>12</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>160</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>1.43939108932709e-05</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>0.0004916400722913762</v>
       </c>
     </row>
@@ -976,39 +1011,42 @@
         <v>30.13947143554687</v>
       </c>
       <c r="D12" t="n">
+        <v>2.478846384</v>
+      </c>
+      <c r="E12" t="n">
         <v>112</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>8</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>3</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>12</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>128</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>0.000154093556416477</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9.606543991623589e-05</v>
       </c>
     </row>
@@ -1023,39 +1061,42 @@
         <v>30.57269096374512</v>
       </c>
       <c r="D13" t="n">
+        <v>2.478846384</v>
+      </c>
+      <c r="E13" t="n">
         <v>112</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>8</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>3</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>12</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>128</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>0.0004300006746231331</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>8.901561151217762e-05</v>
       </c>
     </row>
@@ -1070,39 +1111,42 @@
         <v>30.87657127380371</v>
       </c>
       <c r="D14" t="n">
+        <v>3.77445888</v>
+      </c>
+      <c r="E14" t="n">
         <v>128</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>16</v>
       </c>
-      <c r="F14" t="n">
-        <v>4</v>
-      </c>
       <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
         <v>12</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>192</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>0.0004203332746721646</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>5.851594938999494e-05</v>
       </c>
     </row>
@@ -1117,39 +1161,42 @@
         <v>30.8380729675293</v>
       </c>
       <c r="D15" t="n">
+        <v>3.77445888</v>
+      </c>
+      <c r="E15" t="n">
         <v>128</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>16</v>
       </c>
-      <c r="F15" t="n">
-        <v>4</v>
-      </c>
       <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
         <v>12</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>192</v>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>0.0003325254177414282</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>1.763253332783538e-06</v>
       </c>
     </row>
@@ -1164,39 +1211,42 @@
         <v>30.43733215332031</v>
       </c>
       <c r="D16" t="n">
+        <v>3.77445888</v>
+      </c>
+      <c r="E16" t="n">
         <v>128</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>16</v>
       </c>
-      <c r="F16" t="n">
-        <v>4</v>
-      </c>
       <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="n">
         <v>12</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>192</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>9.318450626771146e-05</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>1.048281105773129e-06</v>
       </c>
     </row>
@@ -1211,39 +1261,42 @@
         <v>30.17931823730469</v>
       </c>
       <c r="D17" t="n">
+        <v>3.77445888</v>
+      </c>
+      <c r="E17" t="n">
         <v>128</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>16</v>
       </c>
-      <c r="F17" t="n">
-        <v>4</v>
-      </c>
       <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
         <v>12</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>192</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>0.0003204806871568567</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>1.046726786164687e-06</v>
       </c>
     </row>
@@ -1258,39 +1311,42 @@
         <v>30.78531341552734</v>
       </c>
       <c r="D18" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="E18" t="n">
         <v>128</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>16</v>
       </c>
-      <c r="F18" t="n">
-        <v>4</v>
-      </c>
       <c r="G18" t="n">
         <v>4</v>
       </c>
       <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="n">
         <v>192</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>0.0004987544765589412</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>2.714567382878084e-06</v>
       </c>
     </row>
@@ -1305,39 +1361,42 @@
         <v>30.7643627166748</v>
       </c>
       <c r="D19" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="E19" t="n">
         <v>128</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>16</v>
       </c>
-      <c r="F19" t="n">
-        <v>4</v>
-      </c>
       <c r="G19" t="n">
         <v>4</v>
       </c>
       <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
         <v>192</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>0.0004991883829785977</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>2.863747303424983e-06</v>
       </c>
     </row>
@@ -1352,39 +1411,42 @@
         <v>30.57999534606934</v>
       </c>
       <c r="D20" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="E20" t="n">
         <v>128</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>16</v>
       </c>
-      <c r="F20" t="n">
-        <v>4</v>
-      </c>
       <c r="G20" t="n">
         <v>4</v>
       </c>
       <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
         <v>192</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>0.0002907239128044456</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>2.117183951892095e-06</v>
       </c>
     </row>
@@ -1399,39 +1461,42 @@
         <v>30.617431640625</v>
       </c>
       <c r="D21" t="n">
+        <v>2.454331824</v>
+      </c>
+      <c r="E21" t="n">
         <v>112</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>16</v>
       </c>
-      <c r="F21" t="n">
-        <v>4</v>
-      </c>
       <c r="G21" t="n">
         <v>4</v>
       </c>
       <c r="H21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" t="n">
         <v>192</v>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>0.0003606201122768387</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>1.976068751266421e-06</v>
       </c>
     </row>
@@ -1446,39 +1511,42 @@
         <v>30.76394500732422</v>
       </c>
       <c r="D22" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="E22" t="n">
         <v>128</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>16</v>
       </c>
-      <c r="F22" t="n">
-        <v>4</v>
-      </c>
       <c r="G22" t="n">
         <v>4</v>
       </c>
       <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="n">
         <v>192</v>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>0.0004421061091630038</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>2.261779313349766e-06</v>
       </c>
     </row>
@@ -1493,39 +1561,42 @@
         <v>30.79811973571777</v>
       </c>
       <c r="D23" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="E23" t="n">
         <v>128</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>16</v>
       </c>
-      <c r="F23" t="n">
-        <v>4</v>
-      </c>
       <c r="G23" t="n">
         <v>4</v>
       </c>
       <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
         <v>192</v>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>0.0004993823063245907</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>3.944834506759931e-06</v>
       </c>
     </row>
@@ -1540,39 +1611,42 @@
         <v>30.42163581848144</v>
       </c>
       <c r="D24" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="E24" t="n">
         <v>128</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>16</v>
       </c>
-      <c r="F24" t="n">
-        <v>4</v>
-      </c>
       <c r="G24" t="n">
         <v>4</v>
       </c>
       <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
         <v>192</v>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>0.00025239477790632</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>4.285156267155689e-06</v>
       </c>
     </row>
@@ -1587,11 +1661,11 @@
         <v>30.66983108520508</v>
       </c>
       <c r="D25" t="n">
+        <v>2.8009827</v>
+      </c>
+      <c r="E25" t="n">
         <v>120</v>
       </c>
-      <c r="E25" t="n">
-        <v>4</v>
-      </c>
       <c r="F25" t="n">
         <v>4</v>
       </c>
@@ -1599,27 +1673,30 @@
         <v>4</v>
       </c>
       <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
         <v>192</v>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>0.0003551075964526897</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>6.447712341895523e-06</v>
       </c>
     </row>
@@ -1634,39 +1711,42 @@
         <v>30.66650581359863</v>
       </c>
       <c r="D26" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="E26" t="n">
         <v>128</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>16</v>
       </c>
-      <c r="F26" t="n">
-        <v>4</v>
-      </c>
       <c r="G26" t="n">
         <v>4</v>
       </c>
       <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="n">
         <v>192</v>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>0.0004789963363422108</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>1.551133644540771e-06</v>
       </c>
     </row>
@@ -1681,39 +1761,42 @@
         <v>30.72971038818359</v>
       </c>
       <c r="D27" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="E27" t="n">
         <v>128</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>16</v>
       </c>
-      <c r="F27" t="n">
-        <v>4</v>
-      </c>
       <c r="G27" t="n">
         <v>4</v>
       </c>
       <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
         <v>192</v>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>0.0004709483890964557</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>2.910704011107e-06</v>
       </c>
     </row>
@@ -1728,39 +1811,42 @@
         <v>30.61976699829102</v>
       </c>
       <c r="D28" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="E28" t="n">
         <v>128</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>16</v>
       </c>
-      <c r="F28" t="n">
-        <v>4</v>
-      </c>
       <c r="G28" t="n">
         <v>4</v>
       </c>
       <c r="H28" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" t="n">
         <v>192</v>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>0.0003840637545701578</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>4.5426890797838e-06</v>
       </c>
     </row>
@@ -1775,39 +1861,42 @@
         <v>30.81734657287598</v>
       </c>
       <c r="D29" t="n">
+        <v>3.170479104</v>
+      </c>
+      <c r="E29" t="n">
         <v>128</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>16</v>
       </c>
-      <c r="F29" t="n">
-        <v>4</v>
-      </c>
       <c r="G29" t="n">
         <v>4</v>
       </c>
       <c r="H29" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" t="n">
         <v>224</v>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>0.0004716123164032875</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>8.543535541086789e-06</v>
       </c>
     </row>
@@ -1822,11 +1911,11 @@
         <v>30.72907943725586</v>
       </c>
       <c r="D30" t="n">
+        <v>2.8009827</v>
+      </c>
+      <c r="E30" t="n">
         <v>120</v>
       </c>
-      <c r="E30" t="n">
-        <v>4</v>
-      </c>
       <c r="F30" t="n">
         <v>4</v>
       </c>
@@ -1834,27 +1923,30 @@
         <v>4</v>
       </c>
       <c r="H30" t="n">
+        <v>4</v>
+      </c>
+      <c r="I30" t="n">
         <v>224</v>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>0.0003217726853306233</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>6.106137196947012e-06</v>
       </c>
     </row>
@@ -1869,39 +1961,42 @@
         <v>30.89419708251953</v>
       </c>
       <c r="D31" t="n">
+        <v>2.652512688</v>
+      </c>
+      <c r="E31" t="n">
         <v>112</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>2</v>
       </c>
-      <c r="F31" t="n">
-        <v>4</v>
-      </c>
       <c r="G31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" t="n">
         <v>8</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>224</v>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>0.0004972096378415374</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>8.920863891956215e-06</v>
       </c>
     </row>
@@ -1916,39 +2011,42 @@
         <v>30.93160247802734</v>
       </c>
       <c r="D32" t="n">
+        <v>3.39697152</v>
+      </c>
+      <c r="E32" t="n">
         <v>128</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>2</v>
       </c>
-      <c r="F32" t="n">
-        <v>4</v>
-      </c>
       <c r="G32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" t="n">
         <v>8</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>224</v>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>0.0004044025880521741</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2.674362183184552e-05</v>
       </c>
     </row>
@@ -1963,39 +2061,42 @@
         <v>30.86603202819824</v>
       </c>
       <c r="D33" t="n">
+        <v>3.01331934</v>
+      </c>
+      <c r="E33" t="n">
         <v>120</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>2</v>
       </c>
-      <c r="F33" t="n">
-        <v>4</v>
-      </c>
       <c r="G33" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" t="n">
         <v>8</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>224</v>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>0.0003954716550020223</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>5.060005315419958e-05</v>
       </c>
     </row>
